--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mint_\Documents\勉強アプリ\理科・社会中１\暗記カードPWA\anki2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586DB4EB-C05A-4594-876D-7E908FEAD250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C3B6CF-5E20-4CD9-8F5C-8CFF3EAD678F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="理科" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="1119">
   <si>
     <t>ID</t>
   </si>
@@ -2763,6 +2763,630 @@
   </si>
   <si>
     <t>s168</t>
+  </si>
+  <si>
+    <t>アブラナの「子房」は、柱頭に花粉がついた（受粉した）あと、何に変化するか。</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>【定番】胚珠（種子になる）とのひっかけに注意。</t>
+  </si>
+  <si>
+    <t>アブラナの「胚珠」は、柱頭に花粉がついた（受粉した）あと、何に変化するか。</t>
+  </si>
+  <si>
+    <t>【定番】子房（果実になる）とのひっかけに注意。</t>
+  </si>
+  <si>
+    <t>マツの枝の先端付近（今年伸びた若い枝の先）についている、赤っぽい小さな雌花が集まったものを何というか。</t>
+  </si>
+  <si>
+    <t>雌花（めばな）</t>
+  </si>
+  <si>
+    <t>【位置注意】雄花は雌花より下（前年の枝の根元付近）につく。</t>
+  </si>
+  <si>
+    <t>マツの雌花のりん片に2づつついており、のちに種子になる部分を何というか。</t>
+  </si>
+  <si>
+    <t>【特徴】マツには子房がなく、胚珠がむき出し。</t>
+  </si>
+  <si>
+    <t>マツの雄花のりん片についており、中に花粉が入っている袋を何というか。</t>
+  </si>
+  <si>
+    <t>【比較】被子植物の「やく」にあたる部分。</t>
+  </si>
+  <si>
+    <t>マツの雌花のりん片と雄花のりん片のうち、のちに「マツカサ（果実のようなもの）」になるのはどちらのりん片が集まったものか。</t>
+  </si>
+  <si>
+    <t>雌花のりん片（A）</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>雌花の胚珠が種子へと成長するのに伴い、りん片全体が硬く大きくなる。</t>
+  </si>
+  <si>
+    <t>マツの花粉には、風に運ばれやすくするためにどのような特徴（つくりの工夫）があるか。</t>
+  </si>
+  <si>
+    <t>空気ぶくろ（空気入れ）がついている</t>
+  </si>
+  <si>
+    <t>【記述対策】風媒介（風媒花）の特徴としてよく出題される。</t>
+  </si>
+  <si>
+    <t>「双眼実体顕微鏡」は、ふつうの顕微鏡と比べて、見え方にどのような違いがあるか。「立体」という言葉を使って答えなさい。</t>
+  </si>
+  <si>
+    <t>対象物を立体的に見ることができる</t>
+  </si>
+  <si>
+    <t>【記述対策】上下左右が逆にならず、そのまま見えるのも特徴。</t>
+  </si>
+  <si>
+    <t>双眼実体顕微鏡のパーツで、直接目をのぞかせる部分のレンズを何というか。</t>
+  </si>
+  <si>
+    <t>接眼レンズ</t>
+  </si>
+  <si>
+    <t>通常の顕微鏡と同様、最初にのぞく場所。</t>
+  </si>
+  <si>
+    <t>双眼実体顕微鏡のパーツで、両目の間隔に合わせて左右のレンズの幅を調節する部分を何というか。</t>
+  </si>
+  <si>
+    <t>視度調節リング</t>
+  </si>
+  <si>
+    <t>左右の視力差を調節する際にも使用する。</t>
+  </si>
+  <si>
+    <t>双眼実体顕微鏡のパーツで、ステージに近い側にある、倍率を変更できるレンズを何というか。</t>
+  </si>
+  <si>
+    <t>対物レンズ</t>
+  </si>
+  <si>
+    <t>倍率の変え方が回転式など通常の顕微鏡と異なる場合がある。</t>
+  </si>
+  <si>
+    <t>種子をつくって仲間をふやす植物を、まとめて何植物というか。</t>
+  </si>
+  <si>
+    <t>すべての植物の基本分類の出発点。</t>
+  </si>
+  <si>
+    <t>種子植物のうち、胚珠が子房の中に包まれている植物を何植物というか。</t>
+  </si>
+  <si>
+    <t>アブラナ、ツツジ、サクラ、ユリ、イネなど。</t>
+  </si>
+  <si>
+    <t>種子植物のうち、子房がなく胚珠がむき出しになっている植物を何植物というか。</t>
+  </si>
+  <si>
+    <t>マツ、イチョウ、ソテツ、スギなど。</t>
+  </si>
+  <si>
+    <t>被子植物のうち、子葉が1枚のグループを何植物というか。</t>
+  </si>
+  <si>
+    <t>ユリ、イネ、トウモロコシなど。</t>
+  </si>
+  <si>
+    <t>被子植物のうち、子葉が2枚のグループを何植物というか。</t>
+  </si>
+  <si>
+    <t>アブラナ、サクラ、ツツジ、タンポポなど。</t>
+  </si>
+  <si>
+    <t>単子葉類の「葉脈（葉のすじ）」の通り方はどのようになっているか。</t>
+  </si>
+  <si>
+    <t>【セットで覚える】子葉1枚＝平行脈＝ひげ根。</t>
+  </si>
+  <si>
+    <t>双子葉類の「葉脈（葉のすじ）」の通り方はどのようになっているか。</t>
+  </si>
+  <si>
+    <t>網状脈（もうじょうみゃく）</t>
+  </si>
+  <si>
+    <t>【セットで覚える】子葉2枚＝網状脈＝主根と側根。</t>
+  </si>
+  <si>
+    <t>単子葉類の「根」の生え方はどのようになっているか。</t>
+  </si>
+  <si>
+    <t>太い根がなく、細い根が多数出ている。</t>
+  </si>
+  <si>
+    <t>双子葉類の「根」の生え方はどのようになっているか。</t>
+  </si>
+  <si>
+    <t>主根と側根</t>
+  </si>
+  <si>
+    <t>中心にある太い「主根」と、そこから枝分かれした「側根」。</t>
+  </si>
+  <si>
+    <t>双子葉類のうち、アブラナやサクラのように花弁（花びら）が1枚ずつ離れているグループを何というか。</t>
+  </si>
+  <si>
+    <t>離弁花類</t>
+  </si>
+  <si>
+    <t>【ひっかけ】ツツジは合弁花類なので注意。</t>
+  </si>
+  <si>
+    <t>双子葉類のうち、ツツジやタンポポのように花弁（花びら）がくっついているグループを何というか。</t>
+  </si>
+  <si>
+    <t>合弁花類</t>
+  </si>
+  <si>
+    <t>【ひっかけ】タンポポは小さな花（合弁花）が多数集まったもの。</t>
+  </si>
+  <si>
+    <t>イヌワラビやゼンマイなどの「シダ植物」は、種子をつくらない代わりに何を使って仲間をふやすか。</t>
+  </si>
+  <si>
+    <t>【特徴】葉・茎・根の区別があり、維管束（通り道）もある。</t>
+  </si>
+  <si>
+    <t>ゼニゴケやスギゴケなどの「コケ植物」は、種子をつくらない代わりに何を使って仲間をふやすか。</t>
+  </si>
+  <si>
+    <t>【ひっかけ】シダ植物と違い、葉・茎・根の区別がなく、維管束もない。</t>
+  </si>
+  <si>
+    <t>コケ植物にある、地面に体を固定し、わずかに水を吸収するための根のようなつくりを何というか。</t>
+  </si>
+  <si>
+    <t>仮根（かこん）</t>
+  </si>
+  <si>
+    <t>【ひっかけ】本物の根ではないため、主に水分は体全体から吸収する。</t>
+  </si>
+  <si>
+    <t>背骨をもたない動物を、まとめて何動物というか。</t>
+  </si>
+  <si>
+    <t>クモ、昆虫、アサリ、イカ、ミミズなど。</t>
+  </si>
+  <si>
+    <t>クモ、ネコ、カナヘビ、メダカ、ワシ、サンショウウオの中で、「一生を水中で生活し、えらで呼吸する」特徴をもつ動物はどれか。</t>
+  </si>
+  <si>
+    <t>メダカ</t>
+  </si>
+  <si>
+    <t>魚類の代表的な特徴。</t>
+  </si>
+  <si>
+    <t>クモ、ネコ、カナヘビ、メダカ、ワシ、サンショウウオの中で、「子はえらと皮膚、親は肺と皮膚で呼吸する」特徴をもつ動物はどれか。</t>
+  </si>
+  <si>
+    <t>サンショウウオ</t>
+  </si>
+  <si>
+    <t>両生類の特徴。変態（成長による変化）を伴う。</t>
+  </si>
+  <si>
+    <t>クモ、ネコ、カナヘビ、メダカ、ワシ、サンショウウオの中で、「体表が乾燥に強い鱗（うろこ）でおおわれている」特徴をもつ動物はどれか。</t>
+  </si>
+  <si>
+    <t>カナヘビ</t>
+  </si>
+  <si>
+    <t>爬虫類の特徴。陸上生活に完全に適応している。</t>
+  </si>
+  <si>
+    <t>クモ、ネコ、カナヘビ、メダカ、ワシ、サンショウウオの中で、親の胎内で一定期間育てられてから生まれる「胎生」の動物はどれか。</t>
+  </si>
+  <si>
+    <t>ネコ</t>
+  </si>
+  <si>
+    <t>哺乳類（哺乳類）の最大の特徴。他はすべて卵生。</t>
+  </si>
+  <si>
+    <t>s169</t>
+  </si>
+  <si>
+    <t>s170</t>
+  </si>
+  <si>
+    <t>s171</t>
+  </si>
+  <si>
+    <t>s172</t>
+  </si>
+  <si>
+    <t>s173</t>
+  </si>
+  <si>
+    <t>s174</t>
+  </si>
+  <si>
+    <t>s175</t>
+  </si>
+  <si>
+    <t>s176</t>
+  </si>
+  <si>
+    <t>s177</t>
+  </si>
+  <si>
+    <t>s178</t>
+  </si>
+  <si>
+    <t>s179</t>
+  </si>
+  <si>
+    <t>s180</t>
+  </si>
+  <si>
+    <t>s181</t>
+  </si>
+  <si>
+    <t>s182</t>
+  </si>
+  <si>
+    <t>s183</t>
+  </si>
+  <si>
+    <t>s184</t>
+  </si>
+  <si>
+    <t>s185</t>
+  </si>
+  <si>
+    <t>s186</t>
+  </si>
+  <si>
+    <t>s187</t>
+  </si>
+  <si>
+    <t>s188</t>
+  </si>
+  <si>
+    <t>s189</t>
+  </si>
+  <si>
+    <t>s190</t>
+  </si>
+  <si>
+    <t>s191</t>
+  </si>
+  <si>
+    <t>s192</t>
+  </si>
+  <si>
+    <t>s193</t>
+  </si>
+  <si>
+    <t>s194</t>
+  </si>
+  <si>
+    <t>s195</t>
+  </si>
+  <si>
+    <t>s196</t>
+  </si>
+  <si>
+    <t>s197</t>
+  </si>
+  <si>
+    <t>s198</t>
+  </si>
+  <si>
+    <t>生命：植物</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>生命：動物</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ガスバーナーに火をつける際、「マッチやライターの火を近づける」のと「ガスのねじをゆるめる」のはどちらが先か。</t>
+  </si>
+  <si>
+    <t>火を近づけるのが先</t>
+  </si>
+  <si>
+    <t>【ひっかけ】先にガスを出すと周囲に引火して危険なため、必ず火を近づけてからねじをゆるめる。</t>
+  </si>
+  <si>
+    <t>ガスバーナーに火をつける正しい手順を、以下の3つの動作の順に答えなさい。「元栓を開ける」「コックを開けてライターに火をつける」「ななめ下から火を近づけガス調節ねじをゆるめる」</t>
+  </si>
+  <si>
+    <t>元栓を開ける → コックを開けてライターに火をつける → ななめ下から火を近づけガス調節ねじをゆるめる</t>
+  </si>
+  <si>
+    <t>手順の並び替え問題として定期テストで非常によく出題される。</t>
+  </si>
+  <si>
+    <t>ガスバーナーの炎が「オレンジ色（黄色）」のとき、空気とガスのどちらが不足している状態か。</t>
+  </si>
+  <si>
+    <t>空気</t>
+  </si>
+  <si>
+    <t>【ひっかけ】炎を青くするためには「空気」を入れる必要がある。</t>
+  </si>
+  <si>
+    <t>ガスバーナーの炎がオレンジ色のとき、上側にある「空気調節ねじ」をどちらの向きに回して調整すればよいか。</t>
+  </si>
+  <si>
+    <t>開く向き（上に回す）</t>
+  </si>
+  <si>
+    <t>【操作注意】下側のガス調節ねじが動かないように押さえながら、上の空気調節ねじを回す。</t>
+  </si>
+  <si>
+    <t>砂糖やかたくり粉のように、加熱すると焦げて炭（炭素）になり、燃えて二酸化炭素を出す物質を何というか。</t>
+  </si>
+  <si>
+    <t>有機物</t>
+  </si>
+  <si>
+    <t>【ひっかけ】食塩は加熱しても焦げず二酸化炭素も出さない（無機物）。</t>
+  </si>
+  <si>
+    <t>食塩や金属のように、有機物以外の物質をまとめて何というか。</t>
+  </si>
+  <si>
+    <t>有機物との違いは「炭素」を含まないこと（一部の例外を除く）。</t>
+  </si>
+  <si>
+    <t>有機物が燃えたときに出てくる気体（二酸化炭素）を確かめるために使用する、白く濁る性質をもつ水溶液は何か。</t>
+  </si>
+  <si>
+    <t>石灰水</t>
+  </si>
+  <si>
+    <t>【定番】「白く濁った＝二酸化炭素が発生した＝元の物質は有機物だった」という一連の流れで覚える。</t>
+  </si>
+  <si>
+    <t>砂糖とかたくり粉はどちらも有機物だが、これらを「水へのとけ方」で区別するとき、水によくとけるのはどちらか。</t>
+  </si>
+  <si>
+    <t>砂糖</t>
+  </si>
+  <si>
+    <t>かたくり粉は水にほとんどとけず白く濁る。</t>
+  </si>
+  <si>
+    <t>金属をみがいたときに、キラリと輝く特有の輝き（光沢）を何というか。</t>
+  </si>
+  <si>
+    <t>【記述】「光る性質」ではなく「金属光沢」と正確に答える。</t>
+  </si>
+  <si>
+    <t>金属に共通する性質（金属光沢、電気を通しやすい、熱を伝えやすい、たたくと広がる・のびる）のうち、「磁石につく」というのは共通の性質といえるか。</t>
+  </si>
+  <si>
+    <t>共通の性質ではない</t>
+  </si>
+  <si>
+    <t>【大不評ひっかけ】鉄は磁石につくが、銅やアルミニウムは磁石につかないため共通ではない。</t>
+  </si>
+  <si>
+    <t>金属の共通の性質で、たたくと薄く広がる性質を「展性」、引っ張ると細くのびる性質を「延性」というが、これらを合わせて何というか。</t>
+  </si>
+  <si>
+    <t>展延性（てんえんせい）</t>
+  </si>
+  <si>
+    <t>「たたくと広がり、引っ張るとのびる」という文章表現で出されることが多い。</t>
+  </si>
+  <si>
+    <t>不規則な形をした金属のかたまりの体積を調べる際、水を入れたある器具に金属を沈めて増えた目盛りを読む。この器具の名前は何か。</t>
+  </si>
+  <si>
+    <t>メスシリンダー</t>
+  </si>
+  <si>
+    <t>水に溶けない固体の体積を測る定番の方法。</t>
+  </si>
+  <si>
+    <t>メスシリンダーの目盛りを読むとき、目の位置は液面に対してどのように合わせるべきか。</t>
+  </si>
+  <si>
+    <t>液面と同じ高さ（水平）にする</t>
+  </si>
+  <si>
+    <t>【記述】上や下からのぞくと正しい値を読み取れない。</t>
+  </si>
+  <si>
+    <t>メスシリンダーに水を入れたとき、液面は中央が少しへこむ。このとき、液面のどの位置の目盛りを読み取るか。</t>
+  </si>
+  <si>
+    <t>最もへこんだ中央の底の位置</t>
+  </si>
+  <si>
+    <t>【ひっかけ】両端の盛り上がった部分ではなく、一番低いところを読む。</t>
+  </si>
+  <si>
+    <t>メスシリンダーの目盛りを読み取るとき、最小目盛りのどこまで目分量で読み取る必要があるか。</t>
+  </si>
+  <si>
+    <t>最小目盛りの10分の1（1/10）まで</t>
+  </si>
+  <si>
+    <t>【厳禁】ぴったりであっても、小数第一位（例: 25.0 cm³）までゼロをつけて読む。</t>
+  </si>
+  <si>
+    <t>物質の「一定の体積（1cm³）あたりの質量」のことを何というか。</t>
+  </si>
+  <si>
+    <t>公式は「密度 ＝ 質量 ÷ 体積」。</t>
+  </si>
+  <si>
+    <t>鉄、銅、アルミニウム、鉛の中で、同じ体積にしたときに最も質量が重い（密度が最も大きい）金属はどれか。</t>
+  </si>
+  <si>
+    <t>鉛</t>
+  </si>
+  <si>
+    <t>鉛の密度は約11.3 g/cm³で、この中では一番大きい。</t>
+  </si>
+  <si>
+    <t>鉄、銅、アルミニウム、鉛の中で、同じ体積にしたときに最も質量が軽い（密度が最も小さい）金属はどれか。</t>
+  </si>
+  <si>
+    <t>アルミニウム</t>
+  </si>
+  <si>
+    <t>アルミニウムの密度は約2.70 g/cm³で、非常に軽い金属。</t>
+  </si>
+  <si>
+    <t>質量が17.9g、体積が2.0cm³の金属片がある。この金属片の密度は何g/cm³か。</t>
+  </si>
+  <si>
+    <t>8.95 g/cm³（または 8.96 g/cm³）</t>
+  </si>
+  <si>
+    <t>【計算】17.9 ÷ 2.0 ＝ 8.95。表のデータ（銅：8.96）に極めて近い。</t>
+  </si>
+  <si>
+    <t>体積が6.0cm³、質量が53.7gの金属片Dがある。この金属片の密度を計算すると約8.95g/cm³となる。この金属片の正体は何か。（鉄:7.87、銅:8.96、アルミ:2.70）</t>
+  </si>
+  <si>
+    <t>銅</t>
+  </si>
+  <si>
+    <t>密度は物質の種類によって決まっているため、計算結果から物質を特定できる。</t>
+  </si>
+  <si>
+    <t>水に氷を入れると浮く。このことから、氷の密度は水の密度と比べて大きいか、小さいか。</t>
+  </si>
+  <si>
+    <t>小さい</t>
+  </si>
+  <si>
+    <t>【基本】密度が小さい（軽い）ものが上に浮き、大きい（重い）ものが下に沈む。</t>
+  </si>
+  <si>
+    <t>エタノールに氷を入れると沈む。このことから、エタノールの密度は氷の密度と比べて大きいか、小さいか。</t>
+  </si>
+  <si>
+    <t>【逆転ひっかけ】水には浮く氷も、エタノールは水より密度が小さいため、氷の方が重くなって沈む。</t>
+  </si>
+  <si>
+    <t>水、エタノール、濃い食塩水のうち、最も密度が大きい（最もものが浮きやすい）液体はどれか。</t>
+  </si>
+  <si>
+    <t>濃い食塩水</t>
+  </si>
+  <si>
+    <t>食塩が溶けている分、普通の水よりも密度が大きくなる。</t>
+  </si>
+  <si>
+    <t>ある物質が「水には沈み、濃い食塩水には浮いた」とする。この物質の密度は、水と濃い食塩水のどちらより大きいか。</t>
+  </si>
+  <si>
+    <t>水の密度より大きい</t>
+  </si>
+  <si>
+    <t>水の密度より大きく、濃い食塩水の密度よりは小さいということになる。</t>
+  </si>
+  <si>
+    <t>サラダ油と酢を混ぜると、サラダ油が上、酢が下に分かれる。この理由を「密度」「小さい」という言葉を使って説明しなさい。</t>
+  </si>
+  <si>
+    <t>サラダ油の密度が、酢の密度よりも小さいから。</t>
+  </si>
+  <si>
+    <t>【記述対策】「軽いから」ではなく「密度が小さいから」と言い換えるのがポイント。</t>
+  </si>
+  <si>
+    <t>s199</t>
+  </si>
+  <si>
+    <t>s200</t>
+  </si>
+  <si>
+    <t>s201</t>
+  </si>
+  <si>
+    <t>s202</t>
+  </si>
+  <si>
+    <t>s203</t>
+  </si>
+  <si>
+    <t>s204</t>
+  </si>
+  <si>
+    <t>s205</t>
+  </si>
+  <si>
+    <t>s206</t>
+  </si>
+  <si>
+    <t>s207</t>
+  </si>
+  <si>
+    <t>s208</t>
+  </si>
+  <si>
+    <t>s209</t>
+  </si>
+  <si>
+    <t>s210</t>
+  </si>
+  <si>
+    <t>s211</t>
+  </si>
+  <si>
+    <t>s212</t>
+  </si>
+  <si>
+    <t>s213</t>
+  </si>
+  <si>
+    <t>s214</t>
+  </si>
+  <si>
+    <t>s215</t>
+  </si>
+  <si>
+    <t>s216</t>
+  </si>
+  <si>
+    <t>s217</t>
+  </si>
+  <si>
+    <t>s218</t>
+  </si>
+  <si>
+    <t>s219</t>
+  </si>
+  <si>
+    <t>s220</t>
+  </si>
+  <si>
+    <t>s221</t>
+  </si>
+  <si>
+    <t>s222</t>
+  </si>
+  <si>
+    <t>s223</t>
+  </si>
+  <si>
+    <t>物質：物質の性質</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -2782,10 +3406,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="6"/>
@@ -3171,7 +3797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I169"/>
+  <dimension ref="A1:I224"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4248,8 +4874,8 @@
       <c r="A77" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>234</v>
+      <c r="B77" s="5" t="s">
+        <v>1118</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>235</v>
@@ -5968,6 +6594,1106 @@
       <c r="G169" s="6"/>
       <c r="H169" s="6"/>
       <c r="I169" s="6"/>
+    </row>
+    <row r="170" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A170" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C170" t="s">
+        <v>912</v>
+      </c>
+      <c r="D170" t="s">
+        <v>27</v>
+      </c>
+      <c r="E170" t="s">
+        <v>913</v>
+      </c>
+      <c r="F170" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A171" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="B171" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C171" t="s">
+        <v>915</v>
+      </c>
+      <c r="D171" t="s">
+        <v>30</v>
+      </c>
+      <c r="E171" t="s">
+        <v>913</v>
+      </c>
+      <c r="F171" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A172" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C172" t="s">
+        <v>917</v>
+      </c>
+      <c r="D172" t="s">
+        <v>918</v>
+      </c>
+      <c r="E172" t="s">
+        <v>913</v>
+      </c>
+      <c r="F172" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A173" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C173" t="s">
+        <v>920</v>
+      </c>
+      <c r="D173" t="s">
+        <v>12</v>
+      </c>
+      <c r="E173" t="s">
+        <v>913</v>
+      </c>
+      <c r="F173" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A174" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C174" t="s">
+        <v>922</v>
+      </c>
+      <c r="D174" t="s">
+        <v>766</v>
+      </c>
+      <c r="E174" t="s">
+        <v>913</v>
+      </c>
+      <c r="F174" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A175" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C175" t="s">
+        <v>924</v>
+      </c>
+      <c r="D175" t="s">
+        <v>925</v>
+      </c>
+      <c r="E175" t="s">
+        <v>926</v>
+      </c>
+      <c r="F175" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A176" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C176" t="s">
+        <v>928</v>
+      </c>
+      <c r="D176" t="s">
+        <v>929</v>
+      </c>
+      <c r="E176" t="s">
+        <v>913</v>
+      </c>
+      <c r="F176" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A177" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C177" t="s">
+        <v>931</v>
+      </c>
+      <c r="D177" t="s">
+        <v>932</v>
+      </c>
+      <c r="E177" t="s">
+        <v>913</v>
+      </c>
+      <c r="F177" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A178" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C178" t="s">
+        <v>934</v>
+      </c>
+      <c r="D178" t="s">
+        <v>935</v>
+      </c>
+      <c r="E178" t="s">
+        <v>913</v>
+      </c>
+      <c r="F178" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A179" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C179" t="s">
+        <v>937</v>
+      </c>
+      <c r="D179" t="s">
+        <v>938</v>
+      </c>
+      <c r="E179" t="s">
+        <v>926</v>
+      </c>
+      <c r="F179" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A180" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C180" t="s">
+        <v>940</v>
+      </c>
+      <c r="D180" t="s">
+        <v>941</v>
+      </c>
+      <c r="E180" t="s">
+        <v>913</v>
+      </c>
+      <c r="F180" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A181" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C181" t="s">
+        <v>943</v>
+      </c>
+      <c r="D181" t="s">
+        <v>36</v>
+      </c>
+      <c r="E181" t="s">
+        <v>913</v>
+      </c>
+      <c r="F181" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A182" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C182" t="s">
+        <v>945</v>
+      </c>
+      <c r="D182" t="s">
+        <v>15</v>
+      </c>
+      <c r="E182" t="s">
+        <v>913</v>
+      </c>
+      <c r="F182" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A183" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C183" t="s">
+        <v>947</v>
+      </c>
+      <c r="D183" t="s">
+        <v>33</v>
+      </c>
+      <c r="E183" t="s">
+        <v>913</v>
+      </c>
+      <c r="F183" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A184" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B184" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C184" t="s">
+        <v>949</v>
+      </c>
+      <c r="D184" t="s">
+        <v>39</v>
+      </c>
+      <c r="E184" t="s">
+        <v>913</v>
+      </c>
+      <c r="F184" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A185" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B185" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C185" t="s">
+        <v>951</v>
+      </c>
+      <c r="D185" t="s">
+        <v>42</v>
+      </c>
+      <c r="E185" t="s">
+        <v>913</v>
+      </c>
+      <c r="F185" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A186" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C186" t="s">
+        <v>953</v>
+      </c>
+      <c r="D186" t="s">
+        <v>48</v>
+      </c>
+      <c r="E186" t="s">
+        <v>913</v>
+      </c>
+      <c r="F186" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A187" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C187" t="s">
+        <v>955</v>
+      </c>
+      <c r="D187" t="s">
+        <v>956</v>
+      </c>
+      <c r="E187" t="s">
+        <v>913</v>
+      </c>
+      <c r="F187" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A188" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C188" t="s">
+        <v>958</v>
+      </c>
+      <c r="D188" t="s">
+        <v>57</v>
+      </c>
+      <c r="E188" t="s">
+        <v>913</v>
+      </c>
+      <c r="F188" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A189" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C189" t="s">
+        <v>960</v>
+      </c>
+      <c r="D189" t="s">
+        <v>961</v>
+      </c>
+      <c r="E189" t="s">
+        <v>913</v>
+      </c>
+      <c r="F189" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A190" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C190" t="s">
+        <v>963</v>
+      </c>
+      <c r="D190" t="s">
+        <v>964</v>
+      </c>
+      <c r="E190" t="s">
+        <v>913</v>
+      </c>
+      <c r="F190" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A191" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C191" t="s">
+        <v>966</v>
+      </c>
+      <c r="D191" t="s">
+        <v>967</v>
+      </c>
+      <c r="E191" t="s">
+        <v>913</v>
+      </c>
+      <c r="F191" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A192" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C192" t="s">
+        <v>969</v>
+      </c>
+      <c r="D192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E192" t="s">
+        <v>913</v>
+      </c>
+      <c r="F192" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A193" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C193" t="s">
+        <v>971</v>
+      </c>
+      <c r="D193" t="s">
+        <v>63</v>
+      </c>
+      <c r="E193" t="s">
+        <v>913</v>
+      </c>
+      <c r="F193" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A194" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C194" t="s">
+        <v>973</v>
+      </c>
+      <c r="D194" t="s">
+        <v>974</v>
+      </c>
+      <c r="E194" t="s">
+        <v>913</v>
+      </c>
+      <c r="F194" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A195" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C195" t="s">
+        <v>976</v>
+      </c>
+      <c r="D195" t="s">
+        <v>96</v>
+      </c>
+      <c r="E195" t="s">
+        <v>913</v>
+      </c>
+      <c r="F195" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A196" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C196" t="s">
+        <v>978</v>
+      </c>
+      <c r="D196" t="s">
+        <v>979</v>
+      </c>
+      <c r="E196" t="s">
+        <v>926</v>
+      </c>
+      <c r="F196" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A197" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C197" t="s">
+        <v>981</v>
+      </c>
+      <c r="D197" t="s">
+        <v>982</v>
+      </c>
+      <c r="E197" t="s">
+        <v>913</v>
+      </c>
+      <c r="F197" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A198" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C198" t="s">
+        <v>984</v>
+      </c>
+      <c r="D198" t="s">
+        <v>985</v>
+      </c>
+      <c r="E198" t="s">
+        <v>913</v>
+      </c>
+      <c r="F198" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A199" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C199" t="s">
+        <v>987</v>
+      </c>
+      <c r="D199" t="s">
+        <v>988</v>
+      </c>
+      <c r="E199" t="s">
+        <v>913</v>
+      </c>
+      <c r="F199" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A200" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C200" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D200" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E200" t="s">
+        <v>913</v>
+      </c>
+      <c r="F200" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A201" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C201" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D201" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E201" t="s">
+        <v>913</v>
+      </c>
+      <c r="F201" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A202" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B202" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D202" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E202" t="s">
+        <v>913</v>
+      </c>
+      <c r="F202" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A203" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B203" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C203" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D203" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E203" t="s">
+        <v>913</v>
+      </c>
+      <c r="F203" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A204" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B204" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C204" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D204" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E204" t="s">
+        <v>913</v>
+      </c>
+      <c r="F204" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A205" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B205" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C205" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D205" t="s">
+        <v>239</v>
+      </c>
+      <c r="E205" t="s">
+        <v>913</v>
+      </c>
+      <c r="F205" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A206" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B206" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D206" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E206" t="s">
+        <v>913</v>
+      </c>
+      <c r="F206" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A207" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B207" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C207" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D207" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E207" t="s">
+        <v>926</v>
+      </c>
+      <c r="F207" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A208" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B208" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C208" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D208" t="s">
+        <v>245</v>
+      </c>
+      <c r="E208" t="s">
+        <v>913</v>
+      </c>
+      <c r="F208" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A209" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B209" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C209" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D209" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E209" t="s">
+        <v>913</v>
+      </c>
+      <c r="F209" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A210" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C210" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D210" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E210" t="s">
+        <v>926</v>
+      </c>
+      <c r="F210" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A211" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B211" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C211" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D211" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E211" t="s">
+        <v>913</v>
+      </c>
+      <c r="F211" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A212" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B212" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C212" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D212" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E212" t="s">
+        <v>913</v>
+      </c>
+      <c r="F212" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A213" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B213" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C213" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D213" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E213" t="s">
+        <v>913</v>
+      </c>
+      <c r="F213" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A214" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B214" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C214" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D214" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E214" t="s">
+        <v>913</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A215" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B215" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C215" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D215" t="s">
+        <v>248</v>
+      </c>
+      <c r="E215" t="s">
+        <v>913</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A216" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B216" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C216" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D216" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E216" t="s">
+        <v>926</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A217" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B217" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C217" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D217" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E217" t="s">
+        <v>913</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A218" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B218" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C218" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D218" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E218" t="s">
+        <v>913</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A219" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B219" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D219" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E219" t="s">
+        <v>913</v>
+      </c>
+      <c r="F219" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A220" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B220" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C220" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D220" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E220" t="s">
+        <v>913</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A221" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B221" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C221" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D221" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E221" t="s">
+        <v>913</v>
+      </c>
+      <c r="F221" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A222" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B222" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C222" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D222" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E222" t="s">
+        <v>913</v>
+      </c>
+      <c r="F222" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A223" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C223" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D223" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E223" t="s">
+        <v>926</v>
+      </c>
+      <c r="F223" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A224" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B224" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C224" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D224" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E224" t="s">
+        <v>913</v>
+      </c>
+      <c r="F224" t="s">
+        <v>1092</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D122" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mint_\Documents\勉強アプリ\理科・社会中１\暗記カードPWA\anki2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C3B6CF-5E20-4CD9-8F5C-8CFF3EAD678F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B81C90-C22C-44F1-A5EA-DE9973F07811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="理科" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="1236">
   <si>
     <t>ID</t>
   </si>
@@ -3386,6 +3386,360 @@
   </si>
   <si>
     <t>物質：物質の性質</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>地球の表面における、陸地と海洋の面積の割合はそれぞれおよそ何％か。</t>
+  </si>
+  <si>
+    <t>陸地：約3割（29％）、海洋：約7割（71％）</t>
+  </si>
+  <si>
+    <t>「陸3：海7」で覚える。定期テスト超頻出。</t>
+  </si>
+  <si>
+    <t>世界にある「６大洋」のうち、最も面積が広い海洋はどこか。</t>
+  </si>
+  <si>
+    <t>ひっかけ注意：大西洋やインド洋と混同しないこと。</t>
+  </si>
+  <si>
+    <t>世界最大の面積を持つ、ユーラシア大陸にある２つの州はどこか。</t>
+  </si>
+  <si>
+    <t>アジア州、ヨーロッパ州</t>
+  </si>
+  <si>
+    <t>１つの大陸に２つの州が存在するひっかけポイント。</t>
+  </si>
+  <si>
+    <t>イギリスの国旗（ユニオンジャック）がデザインの一部に組み込まれている、オセアニア州の主要な国はどこか。</t>
+  </si>
+  <si>
+    <t>オーストラリア（またはニュージーランド）</t>
+  </si>
+  <si>
+    <t>歴史的背景（元イギリス領）から国旗の特徴を問う入試頻出問題。</t>
+  </si>
+  <si>
+    <t>世界で最も面積が大きい国はどこか。</t>
+  </si>
+  <si>
+    <t>ロシア連邦</t>
+  </si>
+  <si>
+    <t>世界最大の国。２位のカナダ、３位のアメリカや中国とも区別しておくこと。</t>
+  </si>
+  <si>
+    <t>周囲をすべて陸地に囲まれ、海に面していない国を何というか。</t>
+  </si>
+  <si>
+    <t>内陸国</t>
+  </si>
+  <si>
+    <t>モンゴルやスイスなどが代表例。島国（日本など）の対義語。</t>
+  </si>
+  <si>
+    <t>古代文明の起源でもあり、現在の国名の由来にもなっているインドを流れる大河の名前は何か。</t>
+  </si>
+  <si>
+    <t>インダス川</t>
+  </si>
+  <si>
+    <t>インダス川がインディア（インド）の語源となった。</t>
+  </si>
+  <si>
+    <t>世界には独立国がおよそ何カ国あるか。</t>
+  </si>
+  <si>
+    <t>約190カ国（約195カ国）</t>
+  </si>
+  <si>
+    <t>「約45カ国」や「約90カ国」といった選択肢のひっかけに注意。</t>
+  </si>
+  <si>
+    <t>北米のアメリカ・カナダ国境やアフリカに見られる、直線的な国境は何を利用して引かれたものか。</t>
+  </si>
+  <si>
+    <t>緯線や経線（数理的国境）</t>
+  </si>
+  <si>
+    <t>山脈や河川などの「自然国境」との違いを記述させる問題も多い。</t>
+  </si>
+  <si>
+    <t>赤道にあたる緯度は何度か。</t>
+  </si>
+  <si>
+    <t>緯度０度</t>
+  </si>
+  <si>
+    <t>緯度の基準。ここから北を北緯、南を南緯という。</t>
+  </si>
+  <si>
+    <t>ロンドンを通る本初子午線にあたる経度は何度か。</t>
+  </si>
+  <si>
+    <t>経度０度</t>
+  </si>
+  <si>
+    <t>経度の基準。イギリスの旧グリニッジ天文台を通る。</t>
+  </si>
+  <si>
+    <t>日本の標準時子午線（東経135度）が通る、兵庫県の都市はどこか。</t>
+  </si>
+  <si>
+    <t>明石市</t>
+  </si>
+  <si>
+    <t>定期テストで漢字指定で非常によく出る。</t>
+  </si>
+  <si>
+    <t>地球は1時間あたり経度で何度自転するか。</t>
+  </si>
+  <si>
+    <t>15度</t>
+  </si>
+  <si>
+    <t>360度÷24時間＝15度。時差の計算の基本。</t>
+  </si>
+  <si>
+    <t>経度0度のロンドンと、東経135度の日本（東京）の時差は何時間か。</t>
+  </si>
+  <si>
+    <t>9時間</t>
+  </si>
+  <si>
+    <t>135÷15＝9時間。日本の方が9時間進んでいる。</t>
+  </si>
+  <si>
+    <t>領土のまわりに設定される、沿岸から12海里までの水域で、沿岸国の主権が及ぶ範囲を何というか。</t>
+  </si>
+  <si>
+    <t>領海</t>
+  </si>
+  <si>
+    <t>排他的経済水域（200海里）との距離のひっかけが超頻出。</t>
+  </si>
+  <si>
+    <t>沿岸から200海里までの水域で、沿岸国が水産資源や鉱産資源を自由に利用できる権利を持つ範囲を何というか。</t>
+  </si>
+  <si>
+    <t>排他的経済水域（EEZ）</t>
+  </si>
+  <si>
+    <t>他国の船の航行自体は禁止できない点がひっかけポイント。</t>
+  </si>
+  <si>
+    <t>日本の島根県に属しているが、現在は韓国によって不法に占拠されている日本固有の領土は何か。</t>
+  </si>
+  <si>
+    <t>竹島</t>
+  </si>
+  <si>
+    <t>尖閣諸島（中国が領有権を主張）、北方領土（ロシアが占拠）とのひっかけに注意。</t>
+  </si>
+  <si>
+    <t>日本最南端の島で、波の侵食によって島が消滅しないよう、政府が周囲をコンクリートの護岸工事で守っている島はどこか。</t>
+  </si>
+  <si>
+    <t>沖ノ鳥島</t>
+  </si>
+  <si>
+    <t>島が消えると排他的経済水域（EEZ）を失ってしまうため護岸工事を行っている。</t>
+  </si>
+  <si>
+    <t>ロシアによって法的根拠なく占拠されている、択捉島、国後島、色丹島、歯舞群島からなる日本固有の領土をまとめて何というか。</t>
+  </si>
+  <si>
+    <t>４つの島・群島名をすべて漢字で書けるようにしておくこと。</t>
+  </si>
+  <si>
+    <t>日本にはいくつの都道府県があるか。</t>
+  </si>
+  <si>
+    <t>ひっかけ注意：「48」などのダミー選択肢に惑わされないこと。</t>
+  </si>
+  <si>
+    <t>都道府県庁が置かれている都市のことを何というか。</t>
+  </si>
+  <si>
+    <t>愛知県（名古屋市）や北海道（札幌市）など、都道府県名と異なる都市名が狙われやすい。</t>
+  </si>
+  <si>
+    <t>世界の気候</t>
+  </si>
+  <si>
+    <t>寒帯の地域において、夏の短い期間だけ氷が溶けて苔（コケ）類が生える気候区を何というか。</t>
+  </si>
+  <si>
+    <t>ツンドラ気候</t>
+  </si>
+  <si>
+    <t>一年中氷に覆われる「氷雪気候」との違いを押さえる。</t>
+  </si>
+  <si>
+    <t>熱帯の気候区のうち、一年中雨が多く降る「熱帯雨林気候」に対し、雨季と乾季がはっきりと分かれている気候区を何というか。</t>
+  </si>
+  <si>
+    <t>サバナ気候</t>
+  </si>
+  <si>
+    <t>まばらな樹木と草原（サバナ）が広がるのが特徴。</t>
+  </si>
+  <si>
+    <t>温帯の気候区のうち、イタリアのローマなどにみられる、夏に乾燥して雨が少なく、冬に雨が降る気候区を何というか。</t>
+  </si>
+  <si>
+    <t>日本（温暖湿潤気候）は夏に雨が多いので、真逆のひっかけとして頻出。</t>
+  </si>
+  <si>
+    <t>乾燥帯の地域において、樹木は育たないが、わずかな雨によって短い草の草原が広がる気候区を何というか。</t>
+  </si>
+  <si>
+    <t>ステップ気候</t>
+  </si>
+  <si>
+    <t>全く雨が降らない「砂漠気候」の一歩手前の気候区。</t>
+  </si>
+  <si>
+    <t>砂漠の周辺などで、過剰な放牧や森林伐採などが原因で、土地がやせて草木が育たなくなる環境問題を何というか。</t>
+  </si>
+  <si>
+    <t>砂漠化</t>
+  </si>
+  <si>
+    <t>アフリカのサハラ砂漠南縁の「サヘル」地域が有名。</t>
+  </si>
+  <si>
+    <t>熱帯や標高の低い地域で見られる、風通しを良くして湿気や害虫を防ぐために床を高くした伝統的な住居を何というか。</t>
+  </si>
+  <si>
+    <t>高床住居（高床式の家）</t>
+  </si>
+  <si>
+    <t>寒冷地の「永久凍土の熱を伝えないための高床」との理由の違いが記述で狙われる。</t>
+  </si>
+  <si>
+    <t>世界の宗教</t>
+  </si>
+  <si>
+    <t>世界の三大宗教のうち、「聖書」を教典とし、日曜日に教会で礼拝を行う宗教は何か。</t>
+  </si>
+  <si>
+    <t>世界で最も信者数が多い。</t>
+  </si>
+  <si>
+    <t>世界三大宗教のうち、「クルアーン（コーラン）」を教典とし、豚肉を食べることや飲酒が禁止されている宗教は何か。</t>
+  </si>
+  <si>
+    <t>信者は「ムスリム」と呼ばれる。</t>
+  </si>
+  <si>
+    <t>インドを中心に信仰され、牛を神の使いとして神聖視するため、牛肉を食べない戒律がある宗教は何か。</t>
+  </si>
+  <si>
+    <t>三大宗教には含まれないが、信者数が多く入試で非常に狙われやすい。</t>
+  </si>
+  <si>
+    <t>g116</t>
+  </si>
+  <si>
+    <t>g117</t>
+  </si>
+  <si>
+    <t>g118</t>
+  </si>
+  <si>
+    <t>g119</t>
+  </si>
+  <si>
+    <t>g120</t>
+  </si>
+  <si>
+    <t>g121</t>
+  </si>
+  <si>
+    <t>g122</t>
+  </si>
+  <si>
+    <t>g123</t>
+  </si>
+  <si>
+    <t>g124</t>
+  </si>
+  <si>
+    <t>g125</t>
+  </si>
+  <si>
+    <t>g126</t>
+  </si>
+  <si>
+    <t>g127</t>
+  </si>
+  <si>
+    <t>g128</t>
+  </si>
+  <si>
+    <t>g129</t>
+  </si>
+  <si>
+    <t>g130</t>
+  </si>
+  <si>
+    <t>g131</t>
+  </si>
+  <si>
+    <t>g132</t>
+  </si>
+  <si>
+    <t>g133</t>
+  </si>
+  <si>
+    <t>g134</t>
+  </si>
+  <si>
+    <t>g135</t>
+  </si>
+  <si>
+    <t>g136</t>
+  </si>
+  <si>
+    <t>g137</t>
+  </si>
+  <si>
+    <t>g138</t>
+  </si>
+  <si>
+    <t>g139</t>
+  </si>
+  <si>
+    <t>g140</t>
+  </si>
+  <si>
+    <t>g141</t>
+  </si>
+  <si>
+    <t>g142</t>
+  </si>
+  <si>
+    <t>g143</t>
+  </si>
+  <si>
+    <t>g144</t>
+  </si>
+  <si>
+    <t>g145</t>
+  </si>
+  <si>
+    <t>世界の姿</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>生活と環境</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>世界の気候</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -7704,7 +8058,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7731,8 +8085,8 @@
       <c r="A2" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>379</v>
+      <c r="B2" s="4" t="s">
+        <v>1233</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>380</v>
@@ -7913,8 +8267,8 @@
       <c r="A15" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>419</v>
+      <c r="B15" s="5" t="s">
+        <v>1234</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>420</v>
@@ -7941,8 +8295,8 @@
       <c r="A17" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>419</v>
+      <c r="B17" s="5" t="s">
+        <v>1235</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>426</v>
@@ -7955,8 +8309,8 @@
       <c r="A18" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>419</v>
+      <c r="B18" s="4" t="s">
+        <v>1235</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>429</v>
@@ -7969,8 +8323,8 @@
       <c r="A19" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>419</v>
+      <c r="B19" s="5" t="s">
+        <v>1235</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>432</v>
@@ -7983,8 +8337,8 @@
       <c r="A20" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>419</v>
+      <c r="B20" s="4" t="s">
+        <v>1235</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>435</v>
@@ -7997,8 +8351,8 @@
       <c r="A21" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>419</v>
+      <c r="B21" s="5" t="s">
+        <v>1235</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>438</v>
@@ -8011,8 +8365,8 @@
       <c r="A22" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>419</v>
+      <c r="B22" s="4" t="s">
+        <v>1235</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>441</v>
@@ -8025,8 +8379,8 @@
       <c r="A23" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>419</v>
+      <c r="B23" s="5" t="s">
+        <v>1235</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>444</v>
@@ -8039,8 +8393,8 @@
       <c r="A24" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>419</v>
+      <c r="B24" s="4" t="s">
+        <v>1235</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>447</v>
@@ -8053,8 +8407,8 @@
       <c r="A25" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>419</v>
+      <c r="B25" s="5" t="s">
+        <v>1235</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>450</v>
@@ -8067,8 +8421,8 @@
       <c r="A26" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>419</v>
+      <c r="B26" s="4" t="s">
+        <v>1235</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>453</v>
@@ -8081,8 +8435,8 @@
       <c r="A27" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>419</v>
+      <c r="B27" s="5" t="s">
+        <v>1235</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>456</v>
@@ -9281,7 +9635,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>724</v>
       </c>
@@ -9295,7 +9649,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>727</v>
       </c>
@@ -9309,7 +9663,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>730</v>
       </c>
@@ -9323,7 +9677,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>733</v>
       </c>
@@ -9335,6 +9689,606 @@
       </c>
       <c r="D116" s="2" t="s">
         <v>736</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A117" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B117" t="s">
+        <v>379</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D117" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E117" t="s">
+        <v>741</v>
+      </c>
+      <c r="F117" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A118" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B118" t="s">
+        <v>379</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D118" t="s">
+        <v>384</v>
+      </c>
+      <c r="E118" t="s">
+        <v>741</v>
+      </c>
+      <c r="F118" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A119" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B119" t="s">
+        <v>379</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E119" t="s">
+        <v>741</v>
+      </c>
+      <c r="F119" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A120" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B120" t="s">
+        <v>379</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E120" t="s">
+        <v>767</v>
+      </c>
+      <c r="F120" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A121" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B121" t="s">
+        <v>379</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E121" t="s">
+        <v>741</v>
+      </c>
+      <c r="F121" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A122" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B122" t="s">
+        <v>379</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D122" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E122" t="s">
+        <v>741</v>
+      </c>
+      <c r="F122" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A123" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B123" t="s">
+        <v>379</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E123" t="s">
+        <v>767</v>
+      </c>
+      <c r="F123" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A124" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B124" t="s">
+        <v>379</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D124" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E124" t="s">
+        <v>741</v>
+      </c>
+      <c r="F124" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A125" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B125" t="s">
+        <v>379</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D125" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E125" t="s">
+        <v>741</v>
+      </c>
+      <c r="F125" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A126" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B126" t="s">
+        <v>379</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E126" t="s">
+        <v>741</v>
+      </c>
+      <c r="F126" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A127" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B127" t="s">
+        <v>379</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D127" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E127" t="s">
+        <v>741</v>
+      </c>
+      <c r="F127" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A128" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B128" t="s">
+        <v>379</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E128" t="s">
+        <v>741</v>
+      </c>
+      <c r="F128" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A129" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B129" t="s">
+        <v>379</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E129" t="s">
+        <v>741</v>
+      </c>
+      <c r="F129" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A130" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B130" t="s">
+        <v>379</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E130" t="s">
+        <v>741</v>
+      </c>
+      <c r="F130" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A131" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B131" t="s">
+        <v>398</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E131" t="s">
+        <v>741</v>
+      </c>
+      <c r="F131" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A132" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B132" t="s">
+        <v>398</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E132" t="s">
+        <v>741</v>
+      </c>
+      <c r="F132" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A133" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B133" t="s">
+        <v>398</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E133" t="s">
+        <v>741</v>
+      </c>
+      <c r="F133" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A134" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B134" t="s">
+        <v>398</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E134" t="s">
+        <v>741</v>
+      </c>
+      <c r="F134" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A135" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B135" t="s">
+        <v>398</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D135" t="s">
+        <v>414</v>
+      </c>
+      <c r="E135" t="s">
+        <v>741</v>
+      </c>
+      <c r="F135" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A136" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B136" t="s">
+        <v>398</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D136">
+        <v>47</v>
+      </c>
+      <c r="E136" t="s">
+        <v>741</v>
+      </c>
+      <c r="F136" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A137" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B137" t="s">
+        <v>398</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D137" t="s">
+        <v>417</v>
+      </c>
+      <c r="E137" t="s">
+        <v>741</v>
+      </c>
+      <c r="F137" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A138" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D138" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E138" t="s">
+        <v>767</v>
+      </c>
+      <c r="F138" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A139" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D139" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E139" t="s">
+        <v>741</v>
+      </c>
+      <c r="F139" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A140" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D140" t="s">
+        <v>433</v>
+      </c>
+      <c r="E140" t="s">
+        <v>741</v>
+      </c>
+      <c r="F140" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A141" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D141" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E141" t="s">
+        <v>767</v>
+      </c>
+      <c r="F141" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A142" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D142" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E142" t="s">
+        <v>741</v>
+      </c>
+      <c r="F142" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A143" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D143" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E143" t="s">
+        <v>767</v>
+      </c>
+      <c r="F143" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A144" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D144" t="s">
+        <v>448</v>
+      </c>
+      <c r="E144" t="s">
+        <v>741</v>
+      </c>
+      <c r="F144" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A145" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D145" t="s">
+        <v>451</v>
+      </c>
+      <c r="E145" t="s">
+        <v>741</v>
+      </c>
+      <c r="F145" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
+      <c r="A146" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D146" t="s">
+        <v>457</v>
+      </c>
+      <c r="E146" t="s">
+        <v>741</v>
+      </c>
+      <c r="F146" t="s">
+        <v>1202</v>
       </c>
     </row>
   </sheetData>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mint_\Documents\勉強アプリ\理科・社会中１\暗記カードPWA\anki2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B81C90-C22C-44F1-A5EA-DE9973F07811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B910D4C5-7040-4EA6-BACD-E500363CB830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="1236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="1233">
   <si>
     <t>ID</t>
   </si>
@@ -1282,9 +1282,6 @@
   </si>
   <si>
     <t>g14</t>
-  </si>
-  <si>
-    <t>生活と環境</t>
   </si>
   <si>
     <t>北極や南極に近い地域など、一年の大半が雪や氷でおおわれ、寒さが厳しい気候帯は何か。</t>
@@ -3620,9 +3617,6 @@
     <t>寒冷地の「永久凍土の熱を伝えないための高床」との理由の違いが記述で狙われる。</t>
   </si>
   <si>
-    <t>世界の宗教</t>
-  </si>
-  <si>
     <t>世界の三大宗教のうち、「聖書」を教典とし、日曜日に教会で礼拝を行う宗教は何か。</t>
   </si>
   <si>
@@ -3732,10 +3726,6 @@
   </si>
   <si>
     <t>世界の姿</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>生活と環境</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -4179,7 +4169,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -4193,7 +4183,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
@@ -4207,7 +4197,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
@@ -4221,7 +4211,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>14</v>
@@ -4235,7 +4225,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
@@ -4249,7 +4239,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -4263,7 +4253,7 @@
         <v>22</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>23</v>
@@ -4277,7 +4267,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>26</v>
@@ -4291,7 +4281,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>29</v>
@@ -4305,7 +4295,7 @@
         <v>31</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>32</v>
@@ -4319,7 +4309,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>35</v>
@@ -4333,7 +4323,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>38</v>
@@ -4347,7 +4337,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>41</v>
@@ -4361,7 +4351,7 @@
         <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>44</v>
@@ -4375,7 +4365,7 @@
         <v>46</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>47</v>
@@ -4389,7 +4379,7 @@
         <v>49</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>50</v>
@@ -4403,7 +4393,7 @@
         <v>52</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>53</v>
@@ -4417,7 +4407,7 @@
         <v>55</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>56</v>
@@ -4431,7 +4421,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>59</v>
@@ -4445,7 +4435,7 @@
         <v>61</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>62</v>
@@ -4459,7 +4449,7 @@
         <v>64</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>65</v>
@@ -4473,7 +4463,7 @@
         <v>67</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>68</v>
@@ -4487,7 +4477,7 @@
         <v>70</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>71</v>
@@ -4501,7 +4491,7 @@
         <v>73</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>74</v>
@@ -4515,7 +4505,7 @@
         <v>76</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>77</v>
@@ -4529,7 +4519,7 @@
         <v>79</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>80</v>
@@ -4543,7 +4533,7 @@
         <v>82</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>83</v>
@@ -4557,7 +4547,7 @@
         <v>85</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>86</v>
@@ -4571,7 +4561,7 @@
         <v>88</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>89</v>
@@ -4585,7 +4575,7 @@
         <v>91</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>92</v>
@@ -4599,7 +4589,7 @@
         <v>94</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>95</v>
@@ -4613,7 +4603,7 @@
         <v>97</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>98</v>
@@ -4627,7 +4617,7 @@
         <v>100</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>101</v>
@@ -4641,7 +4631,7 @@
         <v>103</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>104</v>
@@ -4655,7 +4645,7 @@
         <v>106</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>107</v>
@@ -4669,7 +4659,7 @@
         <v>109</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>110</v>
@@ -4683,7 +4673,7 @@
         <v>112</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>113</v>
@@ -5229,7 +5219,7 @@
         <v>233</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>235</v>
@@ -5870,22 +5860,22 @@
     </row>
     <row r="123" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C123" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="D123" s="7" t="s">
         <v>739</v>
       </c>
-      <c r="D123" s="7" t="s">
+      <c r="E123" s="6" t="s">
         <v>740</v>
       </c>
-      <c r="E123" s="6" t="s">
+      <c r="F123" s="6" t="s">
         <v>741</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>742</v>
       </c>
       <c r="G123" s="6"/>
       <c r="H123" s="6"/>
@@ -5893,22 +5883,22 @@
     </row>
     <row r="124" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C124" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="D124" s="7" t="s">
         <v>743</v>
       </c>
-      <c r="D124" s="7" t="s">
+      <c r="E124" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F124" s="6" t="s">
         <v>744</v>
-      </c>
-      <c r="E124" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>745</v>
       </c>
       <c r="G124" s="6"/>
       <c r="H124" s="6"/>
@@ -5916,22 +5906,22 @@
     </row>
     <row r="125" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C125" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="D125" s="7" t="s">
         <v>746</v>
       </c>
-      <c r="D125" s="7" t="s">
+      <c r="E125" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F125" s="6" t="s">
         <v>747</v>
-      </c>
-      <c r="E125" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>748</v>
       </c>
       <c r="G125" s="6"/>
       <c r="H125" s="6"/>
@@ -5939,22 +5929,22 @@
     </row>
     <row r="126" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C126" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="D126" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="D126" s="7" t="s">
+      <c r="E126" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F126" s="6" t="s">
         <v>750</v>
-      </c>
-      <c r="E126" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F126" s="6" t="s">
-        <v>751</v>
       </c>
       <c r="G126" s="6"/>
       <c r="H126" s="6"/>
@@ -5962,22 +5952,22 @@
     </row>
     <row r="127" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C127" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="D127" s="7" t="s">
         <v>752</v>
       </c>
-      <c r="D127" s="7" t="s">
+      <c r="E127" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F127" s="6" t="s">
         <v>753</v>
-      </c>
-      <c r="E127" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>754</v>
       </c>
       <c r="G127" s="6"/>
       <c r="H127" s="6"/>
@@ -5985,22 +5975,22 @@
     </row>
     <row r="128" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G128" s="6"/>
       <c r="H128" s="6"/>
@@ -6008,22 +5998,22 @@
     </row>
     <row r="129" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G129" s="6"/>
       <c r="H129" s="6"/>
@@ -6031,22 +6021,22 @@
     </row>
     <row r="130" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C130" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="D130" s="7" t="s">
         <v>759</v>
       </c>
-      <c r="D130" s="7" t="s">
+      <c r="E130" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F130" s="6" t="s">
         <v>760</v>
-      </c>
-      <c r="E130" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F130" s="6" t="s">
-        <v>761</v>
       </c>
       <c r="G130" s="6"/>
       <c r="H130" s="6"/>
@@ -6054,22 +6044,22 @@
     </row>
     <row r="131" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C131" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="D131" s="7" t="s">
         <v>762</v>
       </c>
-      <c r="D131" s="7" t="s">
+      <c r="E131" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F131" s="6" t="s">
         <v>763</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F131" s="6" t="s">
-        <v>764</v>
       </c>
       <c r="G131" s="6"/>
       <c r="H131" s="6"/>
@@ -6077,22 +6067,22 @@
     </row>
     <row r="132" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C132" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="D132" s="7" t="s">
         <v>765</v>
       </c>
-      <c r="D132" s="7" t="s">
+      <c r="E132" s="6" t="s">
         <v>766</v>
       </c>
-      <c r="E132" s="6" t="s">
+      <c r="F132" s="6" t="s">
         <v>767</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>768</v>
       </c>
       <c r="G132" s="6"/>
       <c r="H132" s="6"/>
@@ -6100,22 +6090,22 @@
     </row>
     <row r="133" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C133" s="7" t="s">
+        <v>768</v>
+      </c>
+      <c r="D133" s="7" t="s">
         <v>769</v>
       </c>
-      <c r="D133" s="7" t="s">
+      <c r="E133" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="F133" s="6" t="s">
         <v>770</v>
-      </c>
-      <c r="E133" s="6" t="s">
-        <v>767</v>
-      </c>
-      <c r="F133" s="6" t="s">
-        <v>771</v>
       </c>
       <c r="G133" s="6"/>
       <c r="H133" s="6"/>
@@ -6123,22 +6113,22 @@
     </row>
     <row r="134" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C134" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="D134" s="7" t="s">
         <v>772</v>
       </c>
-      <c r="D134" s="7" t="s">
+      <c r="E134" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F134" s="6" t="s">
         <v>773</v>
-      </c>
-      <c r="E134" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>774</v>
       </c>
       <c r="G134" s="6"/>
       <c r="H134" s="6"/>
@@ -6146,22 +6136,22 @@
     </row>
     <row r="135" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D135" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G135" s="6"/>
       <c r="H135" s="6"/>
@@ -6169,22 +6159,22 @@
     </row>
     <row r="136" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D136" s="7" t="s">
         <v>15</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
@@ -6192,22 +6182,22 @@
     </row>
     <row r="137" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D137" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G137" s="6"/>
       <c r="H137" s="6"/>
@@ -6215,22 +6205,22 @@
     </row>
     <row r="138" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C138" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="D138" s="7" t="s">
         <v>781</v>
       </c>
-      <c r="D138" s="7" t="s">
+      <c r="E138" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F138" s="6" t="s">
         <v>782</v>
-      </c>
-      <c r="E138" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>783</v>
       </c>
       <c r="G138" s="6"/>
       <c r="H138" s="6"/>
@@ -6238,22 +6228,22 @@
     </row>
     <row r="139" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D139" s="7" t="s">
         <v>42</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G139" s="6"/>
       <c r="H139" s="6"/>
@@ -6261,22 +6251,22 @@
     </row>
     <row r="140" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C140" s="7" t="s">
+        <v>785</v>
+      </c>
+      <c r="D140" s="7" t="s">
         <v>786</v>
       </c>
-      <c r="D140" s="7" t="s">
+      <c r="E140" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F140" s="6" t="s">
         <v>787</v>
-      </c>
-      <c r="E140" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>788</v>
       </c>
       <c r="G140" s="6"/>
       <c r="H140" s="6"/>
@@ -6284,22 +6274,22 @@
     </row>
     <row r="141" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D141" s="7" t="s">
         <v>57</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="G141" s="6"/>
       <c r="H141" s="6"/>
@@ -6307,22 +6297,22 @@
     </row>
     <row r="142" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D142" s="7" t="s">
         <v>60</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="G142" s="6"/>
       <c r="H142" s="6"/>
@@ -6330,22 +6320,22 @@
     </row>
     <row r="143" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C143" s="7" t="s">
+        <v>792</v>
+      </c>
+      <c r="D143" s="7" t="s">
         <v>793</v>
       </c>
-      <c r="D143" s="7" t="s">
+      <c r="E143" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F143" s="6" t="s">
         <v>794</v>
-      </c>
-      <c r="E143" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>795</v>
       </c>
       <c r="G143" s="6"/>
       <c r="H143" s="6"/>
@@ -6353,22 +6343,22 @@
     </row>
     <row r="144" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>63</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G144" s="6"/>
       <c r="H144" s="6"/>
@@ -6376,22 +6366,22 @@
     </row>
     <row r="145" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C145" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="D145" s="7" t="s">
         <v>798</v>
       </c>
-      <c r="D145" s="7" t="s">
+      <c r="E145" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F145" s="6" t="s">
         <v>799</v>
-      </c>
-      <c r="E145" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>800</v>
       </c>
       <c r="G145" s="6"/>
       <c r="H145" s="6"/>
@@ -6399,22 +6389,22 @@
     </row>
     <row r="146" spans="1:9" ht="39.6" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C146" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="D146" s="7" t="s">
         <v>801</v>
       </c>
-      <c r="D146" s="7" t="s">
+      <c r="E146" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F146" s="6" t="s">
         <v>802</v>
-      </c>
-      <c r="E146" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F146" s="6" t="s">
-        <v>803</v>
       </c>
       <c r="G146" s="6"/>
       <c r="H146" s="6"/>
@@ -6422,22 +6412,22 @@
     </row>
     <row r="147" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C147" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="D147" s="7" t="s">
         <v>804</v>
       </c>
-      <c r="D147" s="7" t="s">
+      <c r="E147" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F147" s="6" t="s">
         <v>805</v>
-      </c>
-      <c r="E147" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>806</v>
       </c>
       <c r="G147" s="6"/>
       <c r="H147" s="6"/>
@@ -6445,22 +6435,22 @@
     </row>
     <row r="148" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C148" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="D148" s="7" t="s">
         <v>807</v>
       </c>
-      <c r="D148" s="7" t="s">
+      <c r="E148" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F148" s="6" t="s">
         <v>808</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>809</v>
       </c>
       <c r="G148" s="6"/>
       <c r="H148" s="6"/>
@@ -6468,22 +6458,22 @@
     </row>
     <row r="149" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C149" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="D149" s="7" t="s">
         <v>810</v>
       </c>
-      <c r="D149" s="7" t="s">
+      <c r="E149" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F149" s="6" t="s">
         <v>811</v>
-      </c>
-      <c r="E149" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>812</v>
       </c>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
@@ -6491,22 +6481,22 @@
     </row>
     <row r="150" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C150" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="D150" s="7" t="s">
         <v>813</v>
       </c>
-      <c r="D150" s="7" t="s">
+      <c r="E150" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F150" s="6" t="s">
         <v>814</v>
-      </c>
-      <c r="E150" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F150" s="6" t="s">
-        <v>815</v>
       </c>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
@@ -6514,22 +6504,22 @@
     </row>
     <row r="151" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C151" s="7" t="s">
+        <v>815</v>
+      </c>
+      <c r="D151" s="7" t="s">
         <v>816</v>
       </c>
-      <c r="D151" s="7" t="s">
+      <c r="E151" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F151" s="6" t="s">
         <v>817</v>
-      </c>
-      <c r="E151" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F151" s="6" t="s">
-        <v>818</v>
       </c>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
@@ -6537,22 +6527,22 @@
     </row>
     <row r="152" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C152" s="7" t="s">
+        <v>818</v>
+      </c>
+      <c r="D152" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="D152" s="7" t="s">
+      <c r="E152" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F152" s="6" t="s">
         <v>820</v>
-      </c>
-      <c r="E152" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F152" s="6" t="s">
-        <v>821</v>
       </c>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
@@ -6560,22 +6550,22 @@
     </row>
     <row r="153" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D153" s="7" t="s">
         <v>72</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
@@ -6583,22 +6573,22 @@
     </row>
     <row r="154" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>84</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
@@ -6606,22 +6596,22 @@
     </row>
     <row r="155" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C155" s="7" t="s">
+        <v>825</v>
+      </c>
+      <c r="D155" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="D155" s="7" t="s">
+      <c r="E155" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="F155" s="6" t="s">
         <v>827</v>
-      </c>
-      <c r="E155" s="6" t="s">
-        <v>767</v>
-      </c>
-      <c r="F155" s="6" t="s">
-        <v>828</v>
       </c>
       <c r="G155" s="6"/>
       <c r="H155" s="6"/>
@@ -6629,22 +6619,22 @@
     </row>
     <row r="156" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C156" s="7" t="s">
+        <v>828</v>
+      </c>
+      <c r="D156" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="D156" s="7" t="s">
+      <c r="E156" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F156" s="6" t="s">
         <v>830</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>831</v>
       </c>
       <c r="G156" s="6"/>
       <c r="H156" s="6"/>
@@ -6652,22 +6642,22 @@
     </row>
     <row r="157" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C157" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="D157" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="D157" s="7" t="s">
+      <c r="E157" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F157" s="6" t="s">
         <v>833</v>
-      </c>
-      <c r="E157" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F157" s="6" t="s">
-        <v>834</v>
       </c>
       <c r="G157" s="6"/>
       <c r="H157" s="6"/>
@@ -6675,22 +6665,22 @@
     </row>
     <row r="158" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C158" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D158" s="7" t="s">
         <v>835</v>
       </c>
-      <c r="D158" s="7" t="s">
+      <c r="E158" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F158" s="6" t="s">
         <v>836</v>
-      </c>
-      <c r="E158" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>837</v>
       </c>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
@@ -6698,22 +6688,22 @@
     </row>
     <row r="159" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C159" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D159" s="7" t="s">
         <v>838</v>
       </c>
-      <c r="D159" s="7" t="s">
+      <c r="E159" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F159" s="6" t="s">
         <v>839</v>
-      </c>
-      <c r="E159" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F159" s="6" t="s">
-        <v>840</v>
       </c>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
@@ -6721,22 +6711,22 @@
     </row>
     <row r="160" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C160" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="D160" s="7" t="s">
         <v>841</v>
       </c>
-      <c r="D160" s="7" t="s">
+      <c r="E160" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F160" s="6" t="s">
         <v>842</v>
-      </c>
-      <c r="E160" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F160" s="6" t="s">
-        <v>843</v>
       </c>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
@@ -6744,22 +6734,22 @@
     </row>
     <row r="161" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C161" s="7" t="s">
+        <v>843</v>
+      </c>
+      <c r="D161" s="7" t="s">
         <v>844</v>
       </c>
-      <c r="D161" s="7" t="s">
+      <c r="E161" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F161" s="6" t="s">
         <v>845</v>
-      </c>
-      <c r="E161" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F161" s="6" t="s">
-        <v>846</v>
       </c>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
@@ -6767,22 +6757,22 @@
     </row>
     <row r="162" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D162" s="7" t="s">
         <v>108</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
@@ -6790,22 +6780,22 @@
     </row>
     <row r="163" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D163" s="7" t="s">
         <v>102</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
@@ -6813,22 +6803,22 @@
     </row>
     <row r="164" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D164" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
@@ -6836,22 +6826,22 @@
     </row>
     <row r="165" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D165" s="7" t="s">
         <v>114</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
@@ -6859,22 +6849,22 @@
     </row>
     <row r="166" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C166" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="D166" s="7" t="s">
         <v>855</v>
       </c>
-      <c r="D166" s="7" t="s">
+      <c r="E166" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="F166" s="6" t="s">
         <v>856</v>
-      </c>
-      <c r="E166" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="F166" s="6" t="s">
-        <v>857</v>
       </c>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
@@ -6882,22 +6872,22 @@
     </row>
     <row r="167" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C167" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="D167" s="7" t="s">
         <v>858</v>
       </c>
-      <c r="D167" s="7" t="s">
+      <c r="E167" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="F167" s="6" t="s">
         <v>859</v>
-      </c>
-      <c r="E167" s="6" t="s">
-        <v>767</v>
-      </c>
-      <c r="F167" s="6" t="s">
-        <v>860</v>
       </c>
       <c r="G167" s="6"/>
       <c r="H167" s="6"/>
@@ -6905,22 +6895,22 @@
     </row>
     <row r="168" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D168" s="7" t="s">
         <v>114</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G168" s="6"/>
       <c r="H168" s="6"/>
@@ -6928,22 +6918,22 @@
     </row>
     <row r="169" spans="1:9" ht="26.4" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D169" s="7" t="s">
         <v>96</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G169" s="6"/>
       <c r="H169" s="6"/>
@@ -6951,1102 +6941,1102 @@
     </row>
     <row r="170" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B170" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C170" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D170" t="s">
         <v>27</v>
       </c>
       <c r="E170" t="s">
+        <v>912</v>
+      </c>
+      <c r="F170" t="s">
         <v>913</v>
-      </c>
-      <c r="F170" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B171" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C171" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D171" t="s">
         <v>30</v>
       </c>
       <c r="E171" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F171" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B172" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C172" t="s">
+        <v>916</v>
+      </c>
+      <c r="D172" t="s">
         <v>917</v>
       </c>
-      <c r="D172" t="s">
+      <c r="E172" t="s">
+        <v>912</v>
+      </c>
+      <c r="F172" t="s">
         <v>918</v>
-      </c>
-      <c r="E172" t="s">
-        <v>913</v>
-      </c>
-      <c r="F172" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B173" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C173" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D173" t="s">
         <v>12</v>
       </c>
       <c r="E173" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F173" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B174" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C174" t="s">
+        <v>921</v>
+      </c>
+      <c r="D174" t="s">
+        <v>765</v>
+      </c>
+      <c r="E174" t="s">
+        <v>912</v>
+      </c>
+      <c r="F174" t="s">
         <v>922</v>
-      </c>
-      <c r="D174" t="s">
-        <v>766</v>
-      </c>
-      <c r="E174" t="s">
-        <v>913</v>
-      </c>
-      <c r="F174" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B175" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C175" t="s">
+        <v>923</v>
+      </c>
+      <c r="D175" t="s">
         <v>924</v>
       </c>
-      <c r="D175" t="s">
+      <c r="E175" t="s">
         <v>925</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
         <v>926</v>
-      </c>
-      <c r="F175" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B176" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C176" t="s">
+        <v>927</v>
+      </c>
+      <c r="D176" t="s">
         <v>928</v>
       </c>
-      <c r="D176" t="s">
+      <c r="E176" t="s">
+        <v>912</v>
+      </c>
+      <c r="F176" t="s">
         <v>929</v>
-      </c>
-      <c r="E176" t="s">
-        <v>913</v>
-      </c>
-      <c r="F176" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B177" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C177" t="s">
+        <v>930</v>
+      </c>
+      <c r="D177" t="s">
         <v>931</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
+        <v>912</v>
+      </c>
+      <c r="F177" t="s">
         <v>932</v>
-      </c>
-      <c r="E177" t="s">
-        <v>913</v>
-      </c>
-      <c r="F177" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B178" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C178" t="s">
+        <v>933</v>
+      </c>
+      <c r="D178" t="s">
         <v>934</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
+        <v>912</v>
+      </c>
+      <c r="F178" t="s">
         <v>935</v>
-      </c>
-      <c r="E178" t="s">
-        <v>913</v>
-      </c>
-      <c r="F178" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B179" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C179" t="s">
+        <v>936</v>
+      </c>
+      <c r="D179" t="s">
         <v>937</v>
       </c>
-      <c r="D179" t="s">
+      <c r="E179" t="s">
+        <v>925</v>
+      </c>
+      <c r="F179" t="s">
         <v>938</v>
-      </c>
-      <c r="E179" t="s">
-        <v>926</v>
-      </c>
-      <c r="F179" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B180" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C180" t="s">
+        <v>939</v>
+      </c>
+      <c r="D180" t="s">
         <v>940</v>
       </c>
-      <c r="D180" t="s">
+      <c r="E180" t="s">
+        <v>912</v>
+      </c>
+      <c r="F180" t="s">
         <v>941</v>
-      </c>
-      <c r="E180" t="s">
-        <v>913</v>
-      </c>
-      <c r="F180" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B181" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C181" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D181" t="s">
         <v>36</v>
       </c>
       <c r="E181" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F181" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B182" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C182" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D182" t="s">
         <v>15</v>
       </c>
       <c r="E182" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F182" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B183" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C183" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D183" t="s">
         <v>33</v>
       </c>
       <c r="E183" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F183" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B184" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C184" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D184" t="s">
         <v>39</v>
       </c>
       <c r="E184" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F184" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B185" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C185" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="D185" t="s">
         <v>42</v>
       </c>
       <c r="E185" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F185" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B186" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C186" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="D186" t="s">
         <v>48</v>
       </c>
       <c r="E186" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F186" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B187" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C187" t="s">
+        <v>954</v>
+      </c>
+      <c r="D187" t="s">
         <v>955</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
+        <v>912</v>
+      </c>
+      <c r="F187" t="s">
         <v>956</v>
-      </c>
-      <c r="E187" t="s">
-        <v>913</v>
-      </c>
-      <c r="F187" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B188" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C188" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D188" t="s">
         <v>57</v>
       </c>
       <c r="E188" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F188" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B189" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C189" t="s">
+        <v>959</v>
+      </c>
+      <c r="D189" t="s">
         <v>960</v>
       </c>
-      <c r="D189" t="s">
+      <c r="E189" t="s">
+        <v>912</v>
+      </c>
+      <c r="F189" t="s">
         <v>961</v>
-      </c>
-      <c r="E189" t="s">
-        <v>913</v>
-      </c>
-      <c r="F189" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B190" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C190" t="s">
+        <v>962</v>
+      </c>
+      <c r="D190" t="s">
         <v>963</v>
       </c>
-      <c r="D190" t="s">
+      <c r="E190" t="s">
+        <v>912</v>
+      </c>
+      <c r="F190" t="s">
         <v>964</v>
-      </c>
-      <c r="E190" t="s">
-        <v>913</v>
-      </c>
-      <c r="F190" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B191" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C191" t="s">
+        <v>965</v>
+      </c>
+      <c r="D191" t="s">
         <v>966</v>
       </c>
-      <c r="D191" t="s">
+      <c r="E191" t="s">
+        <v>912</v>
+      </c>
+      <c r="F191" t="s">
         <v>967</v>
-      </c>
-      <c r="E191" t="s">
-        <v>913</v>
-      </c>
-      <c r="F191" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B192" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C192" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="D192" t="s">
         <v>63</v>
       </c>
       <c r="E192" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F192" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B193" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C193" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D193" t="s">
         <v>63</v>
       </c>
       <c r="E193" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F193" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B194" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C194" t="s">
+        <v>972</v>
+      </c>
+      <c r="D194" t="s">
         <v>973</v>
       </c>
-      <c r="D194" t="s">
+      <c r="E194" t="s">
+        <v>912</v>
+      </c>
+      <c r="F194" t="s">
         <v>974</v>
-      </c>
-      <c r="E194" t="s">
-        <v>913</v>
-      </c>
-      <c r="F194" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B195" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C195" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D195" t="s">
         <v>96</v>
       </c>
       <c r="E195" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F195" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B196" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C196" t="s">
+        <v>977</v>
+      </c>
+      <c r="D196" t="s">
         <v>978</v>
       </c>
-      <c r="D196" t="s">
+      <c r="E196" t="s">
+        <v>925</v>
+      </c>
+      <c r="F196" t="s">
         <v>979</v>
-      </c>
-      <c r="E196" t="s">
-        <v>926</v>
-      </c>
-      <c r="F196" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B197" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C197" t="s">
+        <v>980</v>
+      </c>
+      <c r="D197" t="s">
         <v>981</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" t="s">
+        <v>912</v>
+      </c>
+      <c r="F197" t="s">
         <v>982</v>
-      </c>
-      <c r="E197" t="s">
-        <v>913</v>
-      </c>
-      <c r="F197" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B198" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C198" t="s">
+        <v>983</v>
+      </c>
+      <c r="D198" t="s">
         <v>984</v>
       </c>
-      <c r="D198" t="s">
+      <c r="E198" t="s">
+        <v>912</v>
+      </c>
+      <c r="F198" t="s">
         <v>985</v>
-      </c>
-      <c r="E198" t="s">
-        <v>913</v>
-      </c>
-      <c r="F198" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B199" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C199" t="s">
+        <v>986</v>
+      </c>
+      <c r="D199" t="s">
         <v>987</v>
       </c>
-      <c r="D199" t="s">
+      <c r="E199" t="s">
+        <v>912</v>
+      </c>
+      <c r="F199" t="s">
         <v>988</v>
-      </c>
-      <c r="E199" t="s">
-        <v>913</v>
-      </c>
-      <c r="F199" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B200" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C200" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D200" t="s">
         <v>1022</v>
       </c>
-      <c r="D200" t="s">
+      <c r="E200" t="s">
+        <v>912</v>
+      </c>
+      <c r="F200" t="s">
         <v>1023</v>
-      </c>
-      <c r="E200" t="s">
-        <v>913</v>
-      </c>
-      <c r="F200" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B201" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C201" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D201" t="s">
         <v>1025</v>
       </c>
-      <c r="D201" t="s">
+      <c r="E201" t="s">
+        <v>912</v>
+      </c>
+      <c r="F201" t="s">
         <v>1026</v>
-      </c>
-      <c r="E201" t="s">
-        <v>913</v>
-      </c>
-      <c r="F201" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B202" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C202" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D202" t="s">
         <v>1028</v>
       </c>
-      <c r="D202" t="s">
+      <c r="E202" t="s">
+        <v>912</v>
+      </c>
+      <c r="F202" t="s">
         <v>1029</v>
-      </c>
-      <c r="E202" t="s">
-        <v>913</v>
-      </c>
-      <c r="F202" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B203" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C203" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D203" t="s">
         <v>1031</v>
       </c>
-      <c r="D203" t="s">
+      <c r="E203" t="s">
+        <v>912</v>
+      </c>
+      <c r="F203" t="s">
         <v>1032</v>
-      </c>
-      <c r="E203" t="s">
-        <v>913</v>
-      </c>
-      <c r="F203" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B204" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C204" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D204" t="s">
         <v>1034</v>
       </c>
-      <c r="D204" t="s">
+      <c r="E204" t="s">
+        <v>912</v>
+      </c>
+      <c r="F204" t="s">
         <v>1035</v>
-      </c>
-      <c r="E204" t="s">
-        <v>913</v>
-      </c>
-      <c r="F204" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B205" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C205" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D205" t="s">
         <v>239</v>
       </c>
       <c r="E205" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F205" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B206" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C206" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D206" t="s">
         <v>1039</v>
       </c>
-      <c r="D206" t="s">
+      <c r="E206" t="s">
+        <v>912</v>
+      </c>
+      <c r="F206" t="s">
         <v>1040</v>
-      </c>
-      <c r="E206" t="s">
-        <v>913</v>
-      </c>
-      <c r="F206" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B207" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C207" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D207" t="s">
         <v>1042</v>
       </c>
-      <c r="D207" t="s">
+      <c r="E207" t="s">
+        <v>925</v>
+      </c>
+      <c r="F207" t="s">
         <v>1043</v>
-      </c>
-      <c r="E207" t="s">
-        <v>926</v>
-      </c>
-      <c r="F207" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B208" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C208" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D208" t="s">
         <v>245</v>
       </c>
       <c r="E208" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F208" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B209" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C209" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D209" t="s">
         <v>1047</v>
       </c>
-      <c r="D209" t="s">
+      <c r="E209" t="s">
+        <v>912</v>
+      </c>
+      <c r="F209" t="s">
         <v>1048</v>
-      </c>
-      <c r="E209" t="s">
-        <v>913</v>
-      </c>
-      <c r="F209" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B210" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C210" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D210" t="s">
         <v>1050</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" t="s">
+        <v>925</v>
+      </c>
+      <c r="F210" t="s">
         <v>1051</v>
-      </c>
-      <c r="E210" t="s">
-        <v>926</v>
-      </c>
-      <c r="F210" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B211" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C211" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D211" t="s">
         <v>1053</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" t="s">
+        <v>912</v>
+      </c>
+      <c r="F211" t="s">
         <v>1054</v>
-      </c>
-      <c r="E211" t="s">
-        <v>913</v>
-      </c>
-      <c r="F211" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B212" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C212" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D212" t="s">
         <v>1056</v>
       </c>
-      <c r="D212" t="s">
+      <c r="E212" t="s">
+        <v>912</v>
+      </c>
+      <c r="F212" t="s">
         <v>1057</v>
-      </c>
-      <c r="E212" t="s">
-        <v>913</v>
-      </c>
-      <c r="F212" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B213" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C213" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D213" t="s">
         <v>1059</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
+        <v>912</v>
+      </c>
+      <c r="F213" t="s">
         <v>1060</v>
-      </c>
-      <c r="E213" t="s">
-        <v>913</v>
-      </c>
-      <c r="F213" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B214" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C214" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D214" t="s">
         <v>1062</v>
       </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
+        <v>912</v>
+      </c>
+      <c r="F214" t="s">
         <v>1063</v>
-      </c>
-      <c r="E214" t="s">
-        <v>913</v>
-      </c>
-      <c r="F214" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B215" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C215" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="D215" t="s">
         <v>248</v>
       </c>
       <c r="E215" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F215" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B216" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C216" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D216" t="s">
         <v>1067</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E216" t="s">
+        <v>925</v>
+      </c>
+      <c r="F216" t="s">
         <v>1068</v>
-      </c>
-      <c r="E216" t="s">
-        <v>926</v>
-      </c>
-      <c r="F216" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B217" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C217" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D217" t="s">
         <v>1070</v>
       </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
+        <v>912</v>
+      </c>
+      <c r="F217" t="s">
         <v>1071</v>
-      </c>
-      <c r="E217" t="s">
-        <v>913</v>
-      </c>
-      <c r="F217" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B218" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C218" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D218" t="s">
         <v>1073</v>
       </c>
-      <c r="D218" t="s">
+      <c r="E218" t="s">
+        <v>912</v>
+      </c>
+      <c r="F218" t="s">
         <v>1074</v>
-      </c>
-      <c r="E218" t="s">
-        <v>913</v>
-      </c>
-      <c r="F218" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B219" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C219" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D219" t="s">
         <v>1076</v>
       </c>
-      <c r="D219" t="s">
+      <c r="E219" t="s">
+        <v>912</v>
+      </c>
+      <c r="F219" t="s">
         <v>1077</v>
-      </c>
-      <c r="E219" t="s">
-        <v>913</v>
-      </c>
-      <c r="F219" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="220" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B220" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C220" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D220" t="s">
         <v>1079</v>
       </c>
-      <c r="D220" t="s">
+      <c r="E220" t="s">
+        <v>912</v>
+      </c>
+      <c r="F220" t="s">
         <v>1080</v>
-      </c>
-      <c r="E220" t="s">
-        <v>913</v>
-      </c>
-      <c r="F220" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B221" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C221" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D221" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E221" t="s">
+        <v>912</v>
+      </c>
+      <c r="F221" t="s">
         <v>1082</v>
-      </c>
-      <c r="D221" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E221" t="s">
-        <v>913</v>
-      </c>
-      <c r="F221" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B222" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C222" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D222" t="s">
         <v>1084</v>
       </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
+        <v>912</v>
+      </c>
+      <c r="F222" t="s">
         <v>1085</v>
-      </c>
-      <c r="E222" t="s">
-        <v>913</v>
-      </c>
-      <c r="F222" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B223" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C223" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D223" t="s">
         <v>1087</v>
       </c>
-      <c r="D223" t="s">
+      <c r="E223" t="s">
+        <v>925</v>
+      </c>
+      <c r="F223" t="s">
         <v>1088</v>
-      </c>
-      <c r="E223" t="s">
-        <v>926</v>
-      </c>
-      <c r="F223" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="224" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B224" t="s">
         <v>1117</v>
       </c>
-      <c r="B224" t="s">
-        <v>1118</v>
-      </c>
       <c r="C224" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D224" t="s">
         <v>1090</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
+        <v>912</v>
+      </c>
+      <c r="F224" t="s">
         <v>1091</v>
-      </c>
-      <c r="E224" t="s">
-        <v>913</v>
-      </c>
-      <c r="F224" t="s">
-        <v>1092</v>
       </c>
     </row>
   </sheetData>
@@ -8086,7 +8076,7 @@
         <v>378</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>380</v>
@@ -8268,2027 +8258,2027 @@
         <v>418</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>482</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>488</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>494</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>514</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>520</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>526</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>533</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="3" t="s">
         <v>558</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="C61" s="3" t="s">
+      <c r="D61" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="3" t="s">
         <v>571</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C64" s="2" t="s">
+      <c r="D64" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="C65" s="3" t="s">
+      <c r="D65" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C66" s="2" t="s">
+      <c r="D66" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="C67" s="3" t="s">
+      <c r="D67" s="3" t="s">
         <v>583</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C68" s="2" t="s">
+      <c r="D68" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>589</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C70" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="C71" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>595</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C72" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>601</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C74" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="D75" s="3" t="s">
         <v>608</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C76" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>614</v>
-      </c>
       <c r="D77" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C78" s="2" t="s">
+      <c r="D78" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="3" t="s">
         <v>619</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" s="3" t="s">
         <v>626</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="C82" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>632</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="C84" s="2" t="s">
+      <c r="D84" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="3" t="s">
         <v>638</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C86" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="D86" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="C87" s="3" t="s">
+      <c r="D87" s="3" t="s">
         <v>645</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="C88" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="C89" s="3" t="s">
+      <c r="D89" s="3" t="s">
         <v>651</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="C90" s="2" t="s">
+      <c r="D90" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="C91" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="D91" s="3" t="s">
         <v>658</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="D92" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="C93" s="3" t="s">
+      <c r="D93" s="3" t="s">
         <v>664</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="C94" s="2" t="s">
+      <c r="D94" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="C95" s="3" t="s">
+      <c r="D95" s="3" t="s">
         <v>670</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="D96" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="D97" s="3" t="s">
         <v>677</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="C98" s="2" t="s">
+      <c r="D98" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="C99" s="3" t="s">
+      <c r="D99" s="3" t="s">
         <v>683</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="C100" s="2" t="s">
+      <c r="D100" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="C101" s="3" t="s">
+      <c r="D101" s="3" t="s">
         <v>689</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="C102" s="2" t="s">
+      <c r="D102" s="2" t="s">
         <v>692</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="C103" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="C103" s="3" t="s">
-        <v>696</v>
-      </c>
       <c r="D103" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="C104" s="2" t="s">
+      <c r="D104" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="C105" s="3" t="s">
+      <c r="D105" s="3" t="s">
         <v>701</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="C106" s="2" t="s">
+      <c r="D106" s="2" t="s">
         <v>704</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="C107" s="3" t="s">
+      <c r="D107" s="3" t="s">
         <v>707</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>711</v>
-      </c>
       <c r="D108" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="C109" s="3" t="s">
+      <c r="D109" s="3" t="s">
         <v>713</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="C110" s="2" t="s">
+      <c r="D110" s="2" t="s">
         <v>716</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="B111" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="C111" s="3" t="s">
+      <c r="D111" s="3" t="s">
         <v>719</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="C112" s="2" t="s">
+      <c r="D112" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="B113" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="C113" s="3" t="s">
+      <c r="D113" s="3" t="s">
         <v>725</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="C114" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="B115" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="C115" s="3" t="s">
+      <c r="D115" s="3" t="s">
         <v>731</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="D116" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="B117" t="s">
         <v>379</v>
       </c>
       <c r="C117" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D117" t="s">
         <v>1119</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
+        <v>740</v>
+      </c>
+      <c r="F117" t="s">
         <v>1120</v>
-      </c>
-      <c r="E117" t="s">
-        <v>741</v>
-      </c>
-      <c r="F117" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="B118" t="s">
         <v>379</v>
       </c>
       <c r="C118" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D118" t="s">
         <v>384</v>
       </c>
       <c r="E118" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F118" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="B119" t="s">
         <v>379</v>
       </c>
       <c r="C119" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D119" t="s">
         <v>1124</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
+        <v>740</v>
+      </c>
+      <c r="F119" t="s">
         <v>1125</v>
-      </c>
-      <c r="E119" t="s">
-        <v>741</v>
-      </c>
-      <c r="F119" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="B120" t="s">
         <v>379</v>
       </c>
       <c r="C120" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D120" t="s">
         <v>1127</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
+        <v>766</v>
+      </c>
+      <c r="F120" t="s">
         <v>1128</v>
-      </c>
-      <c r="E120" t="s">
-        <v>767</v>
-      </c>
-      <c r="F120" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="B121" t="s">
         <v>379</v>
       </c>
       <c r="C121" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D121" t="s">
         <v>1130</v>
       </c>
-      <c r="D121" t="s">
+      <c r="E121" t="s">
+        <v>740</v>
+      </c>
+      <c r="F121" t="s">
         <v>1131</v>
-      </c>
-      <c r="E121" t="s">
-        <v>741</v>
-      </c>
-      <c r="F121" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B122" t="s">
         <v>379</v>
       </c>
       <c r="C122" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D122" t="s">
         <v>1133</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
+        <v>740</v>
+      </c>
+      <c r="F122" t="s">
         <v>1134</v>
-      </c>
-      <c r="E122" t="s">
-        <v>741</v>
-      </c>
-      <c r="F122" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="B123" t="s">
         <v>379</v>
       </c>
       <c r="C123" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D123" t="s">
         <v>1136</v>
       </c>
-      <c r="D123" t="s">
+      <c r="E123" t="s">
+        <v>766</v>
+      </c>
+      <c r="F123" t="s">
         <v>1137</v>
-      </c>
-      <c r="E123" t="s">
-        <v>767</v>
-      </c>
-      <c r="F123" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B124" t="s">
         <v>379</v>
       </c>
       <c r="C124" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D124" t="s">
         <v>1139</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
+        <v>740</v>
+      </c>
+      <c r="F124" t="s">
         <v>1140</v>
-      </c>
-      <c r="E124" t="s">
-        <v>741</v>
-      </c>
-      <c r="F124" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="B125" t="s">
         <v>379</v>
       </c>
       <c r="C125" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D125" t="s">
         <v>1142</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
+        <v>740</v>
+      </c>
+      <c r="F125" t="s">
         <v>1143</v>
-      </c>
-      <c r="E125" t="s">
-        <v>741</v>
-      </c>
-      <c r="F125" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B126" t="s">
         <v>379</v>
       </c>
       <c r="C126" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D126" t="s">
         <v>1145</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" t="s">
+        <v>740</v>
+      </c>
+      <c r="F126" t="s">
         <v>1146</v>
-      </c>
-      <c r="E126" t="s">
-        <v>741</v>
-      </c>
-      <c r="F126" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B127" t="s">
         <v>379</v>
       </c>
       <c r="C127" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D127" t="s">
         <v>1148</v>
       </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
+        <v>740</v>
+      </c>
+      <c r="F127" t="s">
         <v>1149</v>
-      </c>
-      <c r="E127" t="s">
-        <v>741</v>
-      </c>
-      <c r="F127" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="B128" t="s">
         <v>379</v>
       </c>
       <c r="C128" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D128" t="s">
         <v>1151</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
+        <v>740</v>
+      </c>
+      <c r="F128" t="s">
         <v>1152</v>
-      </c>
-      <c r="E128" t="s">
-        <v>741</v>
-      </c>
-      <c r="F128" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B129" t="s">
         <v>379</v>
       </c>
       <c r="C129" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D129" t="s">
         <v>1154</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
+        <v>740</v>
+      </c>
+      <c r="F129" t="s">
         <v>1155</v>
-      </c>
-      <c r="E129" t="s">
-        <v>741</v>
-      </c>
-      <c r="F129" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B130" t="s">
         <v>379</v>
       </c>
       <c r="C130" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D130" t="s">
         <v>1157</v>
       </c>
-      <c r="D130" t="s">
+      <c r="E130" t="s">
+        <v>740</v>
+      </c>
+      <c r="F130" t="s">
         <v>1158</v>
-      </c>
-      <c r="E130" t="s">
-        <v>741</v>
-      </c>
-      <c r="F130" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B131" t="s">
         <v>398</v>
       </c>
       <c r="C131" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D131" t="s">
         <v>1160</v>
       </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
+        <v>740</v>
+      </c>
+      <c r="F131" t="s">
         <v>1161</v>
-      </c>
-      <c r="E131" t="s">
-        <v>741</v>
-      </c>
-      <c r="F131" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B132" t="s">
         <v>398</v>
       </c>
       <c r="C132" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D132" t="s">
         <v>1163</v>
       </c>
-      <c r="D132" t="s">
+      <c r="E132" t="s">
+        <v>740</v>
+      </c>
+      <c r="F132" t="s">
         <v>1164</v>
-      </c>
-      <c r="E132" t="s">
-        <v>741</v>
-      </c>
-      <c r="F132" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B133" t="s">
         <v>398</v>
       </c>
       <c r="C133" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D133" t="s">
         <v>1166</v>
       </c>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
+        <v>740</v>
+      </c>
+      <c r="F133" t="s">
         <v>1167</v>
-      </c>
-      <c r="E133" t="s">
-        <v>741</v>
-      </c>
-      <c r="F133" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B134" t="s">
         <v>398</v>
       </c>
       <c r="C134" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D134" t="s">
         <v>1169</v>
       </c>
-      <c r="D134" t="s">
+      <c r="E134" t="s">
+        <v>740</v>
+      </c>
+      <c r="F134" t="s">
         <v>1170</v>
-      </c>
-      <c r="E134" t="s">
-        <v>741</v>
-      </c>
-      <c r="F134" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B135" t="s">
         <v>398</v>
       </c>
       <c r="C135" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="D135" t="s">
         <v>414</v>
       </c>
       <c r="E135" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F135" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B136" t="s">
         <v>398</v>
       </c>
       <c r="C136" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D136">
         <v>47</v>
       </c>
       <c r="E136" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F136" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B137" t="s">
         <v>398</v>
       </c>
       <c r="C137" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="D137" t="s">
         <v>417</v>
       </c>
       <c r="E137" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F137" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B138" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="C138" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D138" t="s">
         <v>1179</v>
       </c>
-      <c r="D138" t="s">
+      <c r="E138" t="s">
+        <v>766</v>
+      </c>
+      <c r="F138" t="s">
         <v>1180</v>
-      </c>
-      <c r="E138" t="s">
-        <v>767</v>
-      </c>
-      <c r="F138" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B139" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C139" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D139" t="s">
         <v>1182</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
+        <v>740</v>
+      </c>
+      <c r="F139" t="s">
         <v>1183</v>
-      </c>
-      <c r="E139" t="s">
-        <v>741</v>
-      </c>
-      <c r="F139" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B140" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C140" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D140" t="s">
+        <v>432</v>
+      </c>
+      <c r="E140" t="s">
+        <v>740</v>
+      </c>
+      <c r="F140" t="s">
         <v>1185</v>
-      </c>
-      <c r="D140" t="s">
-        <v>433</v>
-      </c>
-      <c r="E140" t="s">
-        <v>741</v>
-      </c>
-      <c r="F140" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B141" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C141" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D141" t="s">
         <v>1187</v>
       </c>
-      <c r="D141" t="s">
+      <c r="E141" t="s">
+        <v>766</v>
+      </c>
+      <c r="F141" t="s">
         <v>1188</v>
-      </c>
-      <c r="E141" t="s">
-        <v>767</v>
-      </c>
-      <c r="F141" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="B142" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C142" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D142" t="s">
         <v>1190</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
+        <v>740</v>
+      </c>
+      <c r="F142" t="s">
         <v>1191</v>
-      </c>
-      <c r="E142" t="s">
-        <v>741</v>
-      </c>
-      <c r="F142" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B143" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C143" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D143" t="s">
         <v>1193</v>
       </c>
-      <c r="D143" t="s">
+      <c r="E143" t="s">
+        <v>766</v>
+      </c>
+      <c r="F143" t="s">
         <v>1194</v>
-      </c>
-      <c r="E143" t="s">
-        <v>767</v>
-      </c>
-      <c r="F143" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B144" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D144" t="s">
+        <v>447</v>
+      </c>
+      <c r="E144" t="s">
+        <v>740</v>
+      </c>
+      <c r="F144" t="s">
         <v>1196</v>
-      </c>
-      <c r="C144" t="s">
-        <v>1197</v>
-      </c>
-      <c r="D144" t="s">
-        <v>448</v>
-      </c>
-      <c r="E144" t="s">
-        <v>741</v>
-      </c>
-      <c r="F144" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B145" t="s">
-        <v>1196</v>
+        <v>1177</v>
       </c>
       <c r="C145" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="D145" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E145" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F145" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="13.8" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="B146" t="s">
-        <v>1196</v>
+        <v>1177</v>
       </c>
       <c r="C146" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="D146" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E146" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F146" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
